--- a/output/pdf_financials_xlsx/NANO.xlsx
+++ b/output/pdf_financials_xlsx/NANO.xlsx
@@ -6040,16 +6040,16 @@
         <v>0.391915</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.505915</v>
+        <v>0.1048</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -6064,25 +6064,25 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.911595</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.163224</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.977007</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.20988</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.171841</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.738196</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>8.793246999999999</v>
       </c>
     </row>
     <row r="93">
@@ -10971,7 +10971,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12256,7 +12260,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -14644,7 +14652,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -19652,7 +19664,11 @@
           <t>SHARE−BASED PAYMENTS RESERVE (Note 7)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -21163,7 +21179,11 @@
           <t>SHARE−BASED PAYMENT RESERVE (Note 6) 114,000</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NANO.xlsx
+++ b/output/pdf_financials_xlsx/NANO.xlsx
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002115</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002067</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.008170999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.01197</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.019541</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.028021</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.034002</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.198761</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.924301</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>1.654412</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.7564610000000001</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.250321</v>
       </c>
     </row>
     <row r="13">
@@ -2052,40 +2052,40 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.149923</v>
+        <v>-0.152038</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.652717</v>
+        <v>-0.654784</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.614203</v>
+        <v>-4.622374</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.542558</v>
+        <v>-2.554528</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.699344</v>
+        <v>-2.718885</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.997715</v>
+        <v>-5.025736</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.78118</v>
+        <v>-3.815182</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-11.323108</v>
+        <v>-11.521869</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-15.820764</v>
+        <v>-16.745065</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-31.814883</v>
+        <v>-33.469295</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-29.220022</v>
+        <v>-29.976483</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-11.139843</v>
+        <v>-11.390164</v>
       </c>
     </row>
     <row r="28">
@@ -2172,40 +2172,40 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.149557</v>
+        <v>-0.151672</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.615564</v>
+        <v>-0.617631</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.567093</v>
+        <v>-4.575264</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.4864</v>
+        <v>-2.49837</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.970056</v>
+        <v>-1.989597</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.981725</v>
+        <v>-4.009746</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.301549</v>
+        <v>-3.335551</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.648396</v>
+        <v>-10.847157</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-14.771714</v>
+        <v>-15.696015</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-30.31149</v>
+        <v>-31.965902</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-27.41197</v>
+        <v>-28.168431</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-9.181066</v>
+        <v>-9.431387000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2471,19 +2471,17 @@
       <c r="C34" s="3" t="n">
         <v>1.178726</v>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" s="3" t="n">
+        <v>1.178726</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.970581</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.258592</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.242319</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.153311</v>
@@ -2590,16 +2588,16 @@
         <v>1.186426</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.194231</v>
+        <v>2.372957</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.098019</v>
+        <v>2.0686</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.298592</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.246319</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.153311</v>
@@ -3312,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.390509</v>
+        <v>0.131917</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.246326</v>
+        <v>0.004007</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.013817</v>
@@ -7950,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09550599999999999</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -8010,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09550599999999999</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -17224,7 +17222,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -18763,7 +18761,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -20567,7 +20565,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -36975,7 +36973,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -50589,7 +50591,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -53044,7 +53046,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -56456,7 +56458,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">

--- a/output/pdf_financials_xlsx/NANO.xlsx
+++ b/output/pdf_financials_xlsx/NANO.xlsx
@@ -7217,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.006375</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -36773,7 +36773,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
